--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753713755_individual_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753713755_individual_h_11.xlsx
@@ -658,7 +658,7 @@
         <v>0.008520536396819937</v>
       </c>
       <c r="C2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>47926543</v>
+        <v>3977206</v>
       </c>
       <c r="L2" t="n">
-        <v>25294190</v>
+        <v>1644634</v>
       </c>
       <c r="M2" t="n">
-        <v>5910855</v>
+        <v>338635</v>
       </c>
       <c r="N2" t="n">
-        <v>243895</v>
+        <v>6333</v>
       </c>
       <c r="O2" t="n">
-        <v>3430453</v>
+        <v>179826</v>
       </c>
       <c r="P2" t="n">
-        <v>1299849</v>
+        <v>52627</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999883770942688</v>
+        <v>0.9999812245368958</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8349082469940186</v>
+        <v>0.7206045389175415</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7017713189125061</v>
+        <v>0.5346026420593262</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6188294887542725</v>
+        <v>0.396243691444397</v>
       </c>
       <c r="U2" t="n">
-        <v>0.222100704908371</v>
+        <v>0.0505548007786274</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6803956627845764</v>
+        <v>0.4439479410648346</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7990991473197937</v>
+        <v>0.5918000340461731</v>
       </c>
       <c r="X2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>53079081</v>
+        <v>4775969</v>
       </c>
       <c r="AG2" t="n">
-        <v>33018842</v>
+        <v>3037162</v>
       </c>
       <c r="AH2" t="n">
-        <v>8835934</v>
+        <v>808667</v>
       </c>
       <c r="AI2" t="n">
-        <v>651291</v>
+        <v>59431</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5060281</v>
+        <v>461766</v>
       </c>
       <c r="AK2" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9559435248374939</v>
+        <v>0.9546229243278503</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116207361221313</v>
+        <v>0.912503182888031</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580287098884583</v>
+        <v>0.8579802513122559</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6615698337554932</v>
+        <v>0.6605058908462524</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.901967465877533</v>
+        <v>0.9019959568977356</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314546585083008</v>
+        <v>0.9314878582954407</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002039522590464157</v>
       </c>
       <c r="C3" t="n">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>47926543</v>
+        <v>3977206</v>
       </c>
       <c r="E3" t="n">
-        <v>7226448</v>
+        <v>949006</v>
       </c>
       <c r="F3" t="n">
-        <v>247226</v>
+        <v>53880</v>
       </c>
       <c r="G3" t="n">
-        <v>18274</v>
+        <v>3976</v>
       </c>
       <c r="H3" t="n">
-        <v>14887</v>
+        <v>4229</v>
       </c>
       <c r="I3" t="n">
-        <v>1132</v>
+        <v>394</v>
       </c>
       <c r="J3" t="n">
-        <v>110765007</v>
+        <v>10069501</v>
       </c>
       <c r="K3" t="n">
-        <v>115664602</v>
+        <v>9885229</v>
       </c>
       <c r="L3" t="n">
-        <v>133533612</v>
+        <v>11644361</v>
       </c>
       <c r="M3" t="n">
-        <v>166625327</v>
+        <v>14955639</v>
       </c>
       <c r="N3" t="n">
-        <v>178736312</v>
+        <v>16206956</v>
       </c>
       <c r="O3" t="n">
-        <v>173350444</v>
+        <v>15678187</v>
       </c>
       <c r="P3" t="n">
-        <v>178120661</v>
+        <v>16185768</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8645604252815247</v>
+        <v>0.7972407341003418</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6969397068023682</v>
+        <v>0.4924192428588867</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5733206868171692</v>
+        <v>0.3585780262947083</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2474948167800903</v>
+        <v>0.07028310745954514</v>
       </c>
       <c r="V3" t="n">
-        <v>0.611035943031311</v>
+        <v>0.3508265912532806</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6106749176979065</v>
+        <v>0.2713683247566223</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>53079081</v>
+        <v>4775969</v>
       </c>
       <c r="Z3" t="n">
-        <v>2185497</v>
+        <v>197364</v>
       </c>
       <c r="AA3" t="n">
-        <v>93996</v>
+        <v>8471</v>
       </c>
       <c r="AB3" t="n">
-        <v>75314</v>
+        <v>6869</v>
       </c>
       <c r="AC3" t="n">
-        <v>359</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>330</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>110765820</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>122695174</v>
+        <v>11200265</v>
       </c>
       <c r="AG3" t="n">
-        <v>141081682</v>
+        <v>12784871</v>
       </c>
       <c r="AH3" t="n">
-        <v>168804129</v>
+        <v>15337760</v>
       </c>
       <c r="AI3" t="n">
-        <v>179257373</v>
+        <v>16295346</v>
       </c>
       <c r="AJ3" t="n">
-        <v>174411852</v>
+        <v>15853250</v>
       </c>
       <c r="AK3" t="n">
-        <v>178301599</v>
+        <v>16208790</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575085639953613</v>
+        <v>0.957354724407196</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097797274589539</v>
+        <v>0.9093555212020874</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8570374250411987</v>
+        <v>0.8562913537025452</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6609038710594177</v>
+        <v>0.6595603227615356</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013426303863525</v>
+        <v>0.9008697271347046</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311618804931641</v>
+        <v>0.9308778047561646</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03216441684267991</v>
       </c>
       <c r="C4" t="n">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>8741895</v>
+        <v>1377860</v>
       </c>
       <c r="E4" t="n">
-        <v>25294190</v>
+        <v>1644634</v>
       </c>
       <c r="F4" t="n">
-        <v>1923788</v>
+        <v>255717</v>
       </c>
       <c r="G4" t="n">
-        <v>113032</v>
+        <v>20407</v>
       </c>
       <c r="H4" t="n">
-        <v>199668</v>
+        <v>37045</v>
       </c>
       <c r="I4" t="n">
-        <v>20567</v>
+        <v>4215</v>
       </c>
       <c r="J4" t="n">
-        <v>813</v>
+        <v>119</v>
       </c>
       <c r="K4" t="n">
-        <v>9476821</v>
+        <v>1542057</v>
       </c>
       <c r="L4" t="n">
-        <v>10749162</v>
+        <v>1431733</v>
       </c>
       <c r="M4" t="n">
-        <v>3640815</v>
+        <v>515978</v>
       </c>
       <c r="N4" t="n">
-        <v>854233</v>
+        <v>118937</v>
       </c>
       <c r="O4" t="n">
-        <v>1611397</v>
+        <v>225235</v>
       </c>
       <c r="P4" t="n">
-        <v>326794</v>
+        <v>36300</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999942183494568</v>
+        <v>0.9999906420707703</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8494756817817688</v>
+        <v>0.756987988948822</v>
       </c>
       <c r="S4" t="n">
-        <v>0.699347198009491</v>
+        <v>0.5126446485519409</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5952064990997314</v>
+        <v>0.3764711022377014</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2341111451387405</v>
+        <v>0.05880850553512573</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6438531875610352</v>
+        <v>0.3919318914413452</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6922950744628906</v>
+        <v>0.3721076846122742</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2284621</v>
+        <v>212190</v>
       </c>
       <c r="Z4" t="n">
-        <v>33018842</v>
+        <v>3037162</v>
       </c>
       <c r="AA4" t="n">
-        <v>915390</v>
+        <v>83722</v>
       </c>
       <c r="AB4" t="n">
-        <v>61077</v>
+        <v>5633</v>
       </c>
       <c r="AC4" t="n">
-        <v>12548</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>748</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2446249</v>
+        <v>227021</v>
       </c>
       <c r="AG4" t="n">
-        <v>3201092</v>
+        <v>291223</v>
       </c>
       <c r="AH4" t="n">
-        <v>1462013</v>
+        <v>133857</v>
       </c>
       <c r="AI4" t="n">
-        <v>333172</v>
+        <v>30547</v>
       </c>
       <c r="AJ4" t="n">
-        <v>549989</v>
+        <v>50172</v>
       </c>
       <c r="AK4" t="n">
-        <v>145856</v>
+        <v>13278</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567253589630127</v>
+        <v>0.9559868574142456</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106993675231934</v>
+        <v>0.9109266996383667</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8575327396392822</v>
+        <v>0.857134997844696</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6612366437911987</v>
+        <v>0.6600327491760254</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016548991203308</v>
+        <v>0.9014324545860291</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313082695007324</v>
+        <v>0.9311826825141907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>526234</v>
+        <v>121688</v>
       </c>
       <c r="E5" t="n">
-        <v>2869915</v>
+        <v>359936</v>
       </c>
       <c r="F5" t="n">
-        <v>5910855</v>
+        <v>338635</v>
       </c>
       <c r="G5" t="n">
-        <v>268579</v>
+        <v>32846</v>
       </c>
       <c r="H5" t="n">
-        <v>663018</v>
+        <v>80399</v>
       </c>
       <c r="I5" t="n">
-        <v>71201</v>
+        <v>10862</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7508034</v>
+        <v>1011508</v>
       </c>
       <c r="L5" t="n">
-        <v>10999036</v>
+        <v>1695272</v>
       </c>
       <c r="M5" t="n">
-        <v>4399003</v>
+        <v>605748</v>
       </c>
       <c r="N5" t="n">
-        <v>741560</v>
+        <v>83774</v>
       </c>
       <c r="O5" t="n">
-        <v>2183706</v>
+        <v>332752</v>
       </c>
       <c r="P5" t="n">
-        <v>828696</v>
+        <v>141305</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999954700469971</v>
+        <v>0.9999927282333374</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9059407114982605</v>
+        <v>0.84444659948349</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8795620799064636</v>
+        <v>0.8095148205757141</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9554768204689026</v>
+        <v>0.931668758392334</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9911627769470215</v>
+        <v>0.9876516461372375</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9789833426475525</v>
+        <v>0.9660095572471619</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9936010837554932</v>
+        <v>0.9891809821128845</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>89118</v>
+        <v>8164</v>
       </c>
       <c r="Z5" t="n">
-        <v>946597</v>
+        <v>87570</v>
       </c>
       <c r="AA5" t="n">
-        <v>8835934</v>
+        <v>808667</v>
       </c>
       <c r="AB5" t="n">
-        <v>109931</v>
+        <v>10048</v>
       </c>
       <c r="AC5" t="n">
-        <v>321315</v>
+        <v>29301</v>
       </c>
       <c r="AD5" t="n">
-        <v>6963</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2355496</v>
+        <v>212745</v>
       </c>
       <c r="AG5" t="n">
-        <v>3274384</v>
+        <v>302744</v>
       </c>
       <c r="AH5" t="n">
-        <v>1473924</v>
+        <v>135716</v>
       </c>
       <c r="AI5" t="n">
-        <v>334164</v>
+        <v>30676</v>
       </c>
       <c r="AJ5" t="n">
-        <v>553878</v>
+        <v>50812</v>
       </c>
       <c r="AK5" t="n">
-        <v>146525</v>
+        <v>13405</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734087586402893</v>
+        <v>0.9732111096382141</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641398787498474</v>
+        <v>0.9638177752494812</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983741283416748</v>
+        <v>0.983578622341156</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963043928146362</v>
+        <v>0.9962705373764038</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938869476318359</v>
+        <v>0.993848443031311</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983808398246765</v>
+        <v>0.9983745813369751</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>155846</v>
+        <v>23132</v>
       </c>
       <c r="E6" t="n">
-        <v>203329</v>
+        <v>24882</v>
       </c>
       <c r="F6" t="n">
-        <v>277905</v>
+        <v>25846</v>
       </c>
       <c r="G6" t="n">
-        <v>243895</v>
+        <v>6333</v>
       </c>
       <c r="H6" t="n">
-        <v>94295</v>
+        <v>8841</v>
       </c>
       <c r="I6" t="n">
-        <v>10055</v>
+        <v>1055</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>71955</v>
+        <v>6631</v>
       </c>
       <c r="Z6" t="n">
-        <v>59191</v>
+        <v>5398</v>
       </c>
       <c r="AA6" t="n">
-        <v>120711</v>
+        <v>11132</v>
       </c>
       <c r="AB6" t="n">
-        <v>651291</v>
+        <v>59431</v>
       </c>
       <c r="AC6" t="n">
-        <v>77015</v>
+        <v>7033</v>
       </c>
       <c r="AD6" t="n">
-        <v>5292</v>
+        <v>482</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>118</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>49666</v>
+        <v>17806</v>
       </c>
       <c r="E7" t="n">
-        <v>410341</v>
+        <v>87492</v>
       </c>
       <c r="F7" t="n">
-        <v>1094651</v>
+        <v>156679</v>
       </c>
       <c r="G7" t="n">
-        <v>405091</v>
+        <v>50989</v>
       </c>
       <c r="H7" t="n">
-        <v>3430453</v>
+        <v>179826</v>
       </c>
       <c r="I7" t="n">
-        <v>223839</v>
+        <v>19774</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>247</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8916</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>328269</v>
+        <v>30199</v>
       </c>
       <c r="AB7" t="n">
-        <v>83923</v>
+        <v>7730</v>
       </c>
       <c r="AC7" t="n">
-        <v>5060281</v>
+        <v>461766</v>
       </c>
       <c r="AD7" t="n">
-        <v>132523</v>
+        <v>12065</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>356</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>3180</v>
+        <v>1571</v>
       </c>
       <c r="E8" t="n">
-        <v>39129</v>
+        <v>10417</v>
       </c>
       <c r="F8" t="n">
-        <v>97245</v>
+        <v>23856</v>
       </c>
       <c r="G8" t="n">
-        <v>49257</v>
+        <v>10719</v>
       </c>
       <c r="H8" t="n">
-        <v>639529</v>
+        <v>94721</v>
       </c>
       <c r="I8" t="n">
-        <v>1299849</v>
+        <v>52627</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>891</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3647</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2927</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>138752</v>
+        <v>12696</v>
       </c>
       <c r="AD8" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
